--- a/test-data/subjects-sem2.xlsx
+++ b/test-data/subjects-sem2.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,6 +418,9 @@
       <c r="F1" t="str">
         <v>electiveGroupId</v>
       </c>
+      <c r="G1" t="str">
+        <v>tcp</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -438,6 +441,9 @@
       <c r="F2" t="str">
         <v/>
       </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -458,6 +464,9 @@
       <c r="F3" t="str">
         <v/>
       </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -478,6 +487,9 @@
       <c r="F4" t="str">
         <v/>
       </c>
+      <c r="G4" t="str">
+        <v>yes</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -498,6 +510,9 @@
       <c r="F5" t="str">
         <v/>
       </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -518,6 +533,9 @@
       <c r="F6" t="str">
         <v/>
       </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -538,6 +556,9 @@
       <c r="F7" t="str">
         <v/>
       </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -558,6 +579,9 @@
       <c r="F8" t="str">
         <v/>
       </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -578,6 +602,9 @@
       <c r="F9" t="str">
         <v/>
       </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -598,6 +625,9 @@
       <c r="F10" t="str">
         <v/>
       </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -618,6 +648,9 @@
       <c r="F11" t="str">
         <v/>
       </c>
+      <c r="G11" t="str">
+        <v>yes</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -638,6 +671,9 @@
       <c r="F12" t="str">
         <v/>
       </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -658,6 +694,9 @@
       <c r="F13" t="str">
         <v/>
       </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -678,6 +717,9 @@
       <c r="F14" t="str">
         <v/>
       </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -698,6 +740,9 @@
       <c r="F15" t="str">
         <v/>
       </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -718,6 +763,9 @@
       <c r="F16" t="str">
         <v/>
       </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -738,6 +786,9 @@
       <c r="F17" t="str">
         <v/>
       </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -758,6 +809,9 @@
       <c r="F18" t="str">
         <v/>
       </c>
+      <c r="G18" t="str">
+        <v>yes</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -778,10 +832,13 @@
       <c r="F19" t="str">
         <v/>
       </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
   </ignoredErrors>
 </worksheet>
 </file>